--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="45">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -132,6 +132,21 @@
   </si>
   <si>
     <t>Kawasaki Ninja 650 Gets Discount worth Rs. 27,000</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 17:29:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 17:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 17:37:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 17:39:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 17:44:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -178,11 +193,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="6.28125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="75.09765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.28125" customWidth="true" bestFit="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
@@ -203,7 +213,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -214,7 +224,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -225,7 +235,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -236,7 +246,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -247,7 +257,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -258,7 +268,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -269,7 +279,7 @@
         <v>17</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -280,7 +290,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -291,7 +301,7 @@
         <v>21</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -302,7 +312,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -313,7 +323,7 @@
         <v>25</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -324,7 +334,7 @@
         <v>27</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -335,7 +345,7 @@
         <v>29</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -346,7 +356,7 @@
         <v>31</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -357,7 +367,7 @@
         <v>33</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -368,7 +378,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -379,7 +389,7 @@
         <v>37</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -390,7 +400,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet_2" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet_5" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="92">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -613,4 +614,289 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="News_Report" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet_2" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="53">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -147,6 +148,30 @@
   </si>
   <si>
     <t>Wed Feb 25 17:44:10 IST 2026</t>
+  </si>
+  <si>
+    <t>All-new Ducati DesertX unveiled</t>
+  </si>
+  <si>
+    <t>KTM RC 160 Launched in New Colours</t>
+  </si>
+  <si>
+    <t>KTM 250 Duke Available In Three Colours</t>
+  </si>
+  <si>
+    <t>Triumph 350cc Motorcycles To Launch in April 2026</t>
+  </si>
+  <si>
+    <t>Indian Motorcycle Releases Limited-Run Models Celebrating 125th Anniversary</t>
+  </si>
+  <si>
+    <t>KTM 990 RC R Track Unveiled: More Powerful Than Before</t>
+  </si>
+  <si>
+    <t>Is Michelin Anakee Adventure 2 a Smarter Tyre for Serious Adventure Riders?</t>
+  </si>
+  <si>
+    <t>KTM 390 Adventure Range Accessories Offer Extended</t>
   </si>
 </sst>
 </file>
@@ -406,4 +431,166 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2464113_cognizant_com/Documents/Desktop/IdentifyingBikes/ExcelData/"/>
     </mc:Choice>
@@ -13,14 +13,14 @@
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_5" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet_5" r:id="rId5" sheetId="1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="64">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -218,6 +218,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -582,290 +583,286 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5">
+      <c r="A5" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6">
+      <c r="A6" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8">
+      <c r="A8" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9">
+      <c r="A9" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10">
+      <c r="A10" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11">
+      <c r="A11" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12">
+      <c r="A12" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="0">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13">
+      <c r="A13" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="0">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14">
+      <c r="A14" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="0">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15">
+      <c r="A15" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="0">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16">
+      <c r="A16" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="0">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17">
+      <c r="A17" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="0">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="18">
+      <c r="A18" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="0">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19">
+      <c r="A19" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="0">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="20">
+      <c r="A20" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="0">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="21">
+      <c r="A21" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="0">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="22">
+      <c r="A22" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="0">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23">
+      <c r="A23" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="0">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="24">
+      <c r="A24" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="0">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="25">
+      <c r="A25" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="0">
         <v>43</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="57">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -172,6 +172,18 @@
   </si>
   <si>
     <t>KTM 390 Adventure Range Accessories Offer Extended</t>
+  </si>
+  <si>
+    <t>Raptee.HV T30 electric motorcycle deliveries commence</t>
+  </si>
+  <si>
+    <t>Triumph Turns its 2026 Triple Trophy Prize into Collector Editions</t>
+  </si>
+  <si>
+    <t>KTM RC 160 Available in Three Colour Options</t>
+  </si>
+  <si>
+    <t>Suzuki announces Motofest campaign</t>
   </si>
 </sst>
 </file>
@@ -451,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -459,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +479,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +487,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -483,7 +495,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +503,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +511,7 @@
         <v>16</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -507,7 +519,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +527,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -523,7 +535,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -531,7 +543,7 @@
         <v>24</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +551,7 @@
         <v>26</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>11</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -547,7 +559,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +567,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -563,7 +575,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -571,7 +583,7 @@
         <v>34</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -579,7 +591,7 @@
         <v>36</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -587,7 +599,7 @@
         <v>38</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
   <si>
     <t>Sr. No.</t>
   </si>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="14">
   <si>
     <t>Sr. No</t>
   </si>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="23">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>NAME: Bajaj Avenger Street 160 | RATING: 4.4/5 (151 Ratings) | SPECS: 160 cc|45 kmpl|14.79 bhp|156 kg | PRICE: ₹ 1,12,280</t>
+  </si>
+  <si>
+    <t>NAME: Bajaj Pulsar N250 | RATING: 4.6/5 (100 Ratings) | SPECS: 249 cc|44 kmpl|24.1 bhp|162 kg | PRICE: ₹ 1,34,758</t>
   </si>
 </sst>
 </file>
@@ -165,7 +168,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -173,7 +176,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -181,7 +184,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -189,7 +192,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -205,7 +208,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -285,7 +288,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -293,7 +296,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="60">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>Suzuki announces Motofest campaign</t>
+  </si>
+  <si>
+    <t>MotoGP 2026: KTM's Pedro Acosta wins Thailand Grand Prix Sprint</t>
+  </si>
+  <si>
+    <t>Your Weekly Dose of Bike Updates: KTM RC 160, Suzuki E Access, and More!</t>
+  </si>
+  <si>
+    <t>Updated KTM 200 Duke: What Is New?</t>
   </si>
 </sst>
 </file>
@@ -463,7 +472,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +480,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -479,7 +488,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +496,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +504,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -503,7 +512,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +520,7 @@
         <v>16</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -519,7 +528,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +536,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -535,7 +544,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -543,7 +552,7 @@
         <v>24</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -551,7 +560,7 @@
         <v>26</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -559,7 +568,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -567,7 +576,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +584,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +592,7 @@
         <v>34</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -591,7 +600,7 @@
         <v>36</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -599,7 +608,7 @@
         <v>38</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="81">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -212,6 +212,57 @@
   </si>
   <si>
     <t>2021 Suzuki Gixxer Special Edition</t>
+  </si>
+  <si>
+    <t>2016 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>₹ 48,500</t>
+  </si>
+  <si>
+    <t>₹ 70,000</t>
+  </si>
+  <si>
+    <t>2020 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>2020 Suzuki Gixxer Standard - BS IV</t>
+  </si>
+  <si>
+    <t>₹ 1.2 Lakh</t>
+  </si>
+  <si>
+    <t>2021 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>2015 Suzuki Gixxer Standard - BS4</t>
+  </si>
+  <si>
+    <t>₹ 35,000</t>
+  </si>
+  <si>
+    <t>2024 Suzuki Gixxer Ride Connect</t>
+  </si>
+  <si>
+    <t>₹ 1.25 Lakh</t>
+  </si>
+  <si>
+    <t>2024 Suzuki Gixxer Ride Connect [2023-2024]</t>
+  </si>
+  <si>
+    <t>₹ 1.55 Lakh</t>
+  </si>
+  <si>
+    <t>₹ 95,000</t>
+  </si>
+  <si>
+    <t>2015 Suzuki Gixxer Rear Drum</t>
+  </si>
+  <si>
+    <t>₹ 20,000</t>
+  </si>
+  <si>
+    <t>2015 Suzuki Gixxer Single Channel ABS - BS4</t>
   </si>
 </sst>
 </file>
@@ -603,10 +654,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>41</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -614,10 +665,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -625,10 +676,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -636,10 +687,10 @@
         <v>9</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>32</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -647,10 +698,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -658,10 +709,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>15</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -669,10 +720,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -680,10 +731,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -691,10 +742,10 @@
         <v>18</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +753,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -713,10 +764,10 @@
         <v>21</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -724,10 +775,10 @@
         <v>22</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -735,10 +786,10 @@
         <v>23</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -746,10 +797,10 @@
         <v>24</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +808,10 @@
         <v>25</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -768,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -779,10 +830,10 @@
         <v>28</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -790,10 +841,10 @@
         <v>29</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -801,10 +852,10 @@
         <v>30</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
@@ -812,10 +863,10 @@
         <v>33</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -823,10 +874,10 @@
         <v>35</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -834,10 +885,10 @@
         <v>36</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -845,10 +896,10 @@
         <v>37</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -856,10 +907,10 @@
         <v>38</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
   <si>
     <t>Sr. No</t>
   </si>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="14">
   <si>
     <t>Sr. No</t>
   </si>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="124">
   <si>
     <t>Sr.No</t>
   </si>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,14 +6,15 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId4" sheetId="2"/>
-    <sheet name="Sheet_3" r:id="rId5" sheetId="3"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="5"/>
+    <sheet name="Sheet_3" r:id="rId5" sheetId="6"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="102">
   <si>
     <t>Sr. No</t>
   </si>
@@ -157,6 +158,168 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Bike Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>2022 Suzuki Gixxer Single Channel ABS</t>
+  </si>
+  <si>
+    <t>₹ 99,900</t>
+  </si>
+  <si>
+    <t>2017 Suzuki Gixxer Single Channel ABS</t>
+  </si>
+  <si>
+    <t>₹ 50,000</t>
+  </si>
+  <si>
+    <t>2021 Suzuki Gixxer Single Channel ABS - BS4</t>
+  </si>
+  <si>
+    <t>₹ 80,000</t>
+  </si>
+  <si>
+    <t>2014 Suzuki Gixxer Ride Connect</t>
+  </si>
+  <si>
+    <t>₹ 38,000</t>
+  </si>
+  <si>
+    <t>2023 Suzuki Gixxer Ride Connect</t>
+  </si>
+  <si>
+    <t>₹ 90,000</t>
+  </si>
+  <si>
+    <t>2019 Suzuki Gixxer ABS</t>
+  </si>
+  <si>
+    <t>₹ 1.1 Lakh</t>
+  </si>
+  <si>
+    <t>2022 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>2017 Suzuki Gixxer Dual Tone Rear Disc</t>
+  </si>
+  <si>
+    <t>₹ 55,000</t>
+  </si>
+  <si>
+    <t>2016 Suzuki Gixxer Dual Tone</t>
+  </si>
+  <si>
+    <t>₹ 45,000</t>
+  </si>
+  <si>
+    <t>₹ 1.4 Lakh</t>
+  </si>
+  <si>
+    <t>2019 Suzuki Gixxer Single Channel ABS</t>
+  </si>
+  <si>
+    <t>₹ 48,000</t>
+  </si>
+  <si>
+    <t>2014 Suzuki Gixxer Single Channel ABS</t>
+  </si>
+  <si>
+    <t>₹ 40,000</t>
+  </si>
+  <si>
+    <t>2020 Suzuki Gixxer Special Edition</t>
+  </si>
+  <si>
+    <t>₹ 1 Lakh</t>
+  </si>
+  <si>
+    <t>2021 Suzuki Gixxer ABS</t>
+  </si>
+  <si>
+    <t>2015 Suzuki Gixxer Single Channel ABS</t>
+  </si>
+  <si>
+    <t>₹ 25,000</t>
+  </si>
+  <si>
+    <t>2018 Suzuki Gixxer Single Channel ABS - BS4</t>
+  </si>
+  <si>
+    <t>2017 Suzuki Gixxer Standard - BS4</t>
+  </si>
+  <si>
+    <t>₹ 42,000</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>2017 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>₹ 41,000</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2015 Suzuki Gixxer Ride Connect</t>
+  </si>
+  <si>
+    <t>₹ 60,000</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>2024 Suzuki Gixxer Ride Connect Special Edition - OBD 2B</t>
+  </si>
+  <si>
+    <t>₹ 1.3 Lakh</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2021 Suzuki Gixxer Special Edition</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>₹ 95,000</t>
+  </si>
+  <si>
+    <t>2021 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>2015 Suzuki Gixxer Standard - BS4</t>
+  </si>
+  <si>
+    <t>₹ 35,000</t>
+  </si>
+  <si>
+    <t>2024 Suzuki Gixxer Ride Connect</t>
+  </si>
+  <si>
+    <t>₹ 1.25 Lakh</t>
+  </si>
+  <si>
+    <t>2024 Suzuki Gixxer Ride Connect [2023-2024]</t>
+  </si>
+  <si>
+    <t>₹ 1.55 Lakh</t>
+  </si>
+  <si>
+    <t>2020 Suzuki Gixxer Standard</t>
   </si>
 </sst>
 </file>
@@ -199,7 +362,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -361,7 +524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -379,7 +542,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -387,7 +550,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -395,7 +558,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +566,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -411,7 +574,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -419,7 +582,292 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>47</v>
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,17 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="10"/>
     <sheet name="Sheet_3" r:id="rId5" sheetId="11"/>
     <sheet name="Sheet_4" r:id="rId8" sheetId="12"/>
     <sheet name="Sheet_5" r:id="rId6" sheetId="13"/>
+    <sheet name="Sheet1" r:id="rId9" sheetId="14"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="291">
   <si>
     <t>Sr. No</t>
   </si>
@@ -645,6 +646,249 @@
   </si>
   <si>
     <t>2015 Suzuki Gixxer Single Channel ABS - BS4</t>
+  </si>
+  <si>
+    <t>Rating/Reviews</t>
+  </si>
+  <si>
+    <t>Specs</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar N160</t>
+  </si>
+  <si>
+    <t>4.6/5 (285 Ratings)</t>
+  </si>
+  <si>
+    <t>164.82 cc|51.6 kmpl|15.68 bhp|152 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,14,840</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar NS200</t>
+  </si>
+  <si>
+    <t>4.7/5 (977 Ratings)</t>
+  </si>
+  <si>
+    <t>199.5 cc|36 kmpl|24.13 bhp|158 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,34,162</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar 125</t>
+  </si>
+  <si>
+    <t>4.4/5 (390 Ratings)</t>
+  </si>
+  <si>
+    <t>124.4 cc|50 kmpl|11.64 bhp|140 kg</t>
+  </si>
+  <si>
+    <t>₹ 82,420</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar NS125</t>
+  </si>
+  <si>
+    <t>4.5/5 (160 Ratings)</t>
+  </si>
+  <si>
+    <t>124.45 cc|46.9 kmpl|11.8 bhp|144 kg</t>
+  </si>
+  <si>
+    <t>₹ 92,671</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar NS400Z</t>
+  </si>
+  <si>
+    <t>4.6/5 (106 Ratings)</t>
+  </si>
+  <si>
+    <t>373 cc|32 kmpl|42.41 bhp|174 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,94,061</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar NS160</t>
+  </si>
+  <si>
+    <t>4.6/5 (467 Ratings)</t>
+  </si>
+  <si>
+    <t>160.3 cc|52.2 kmpl|17.03 bhp|152 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,21,837</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar 150</t>
+  </si>
+  <si>
+    <t>4.5/5 (1428 Ratings)</t>
+  </si>
+  <si>
+    <t>149.5 cc|49 kmpl|13.8 bhp|148 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,10,120</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>Bajaj Chetak (3.8/5)</t>
+  </si>
+  <si>
+    <t>182 Ratings</t>
+  </si>
+  <si>
+    <t>73 kmph|153 km|3.5 kWh</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar N250</t>
+  </si>
+  <si>
+    <t>4.6/5 (100 Ratings)</t>
+  </si>
+  <si>
+    <t>249 cc|44 kmpl|24.1 bhp|162 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,34,758</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar RS 200</t>
+  </si>
+  <si>
+    <t>4.7/5 (632 Ratings)</t>
+  </si>
+  <si>
+    <t>199.5 cc|35 kmpl|24.1 bhp|167 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,72,857</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar 220 F</t>
+  </si>
+  <si>
+    <t>4.7/5 (92 Ratings)</t>
+  </si>
+  <si>
+    <t>220 cc|40 kmpl|20.11 bhp|160 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,27,481</t>
+  </si>
+  <si>
+    <t>Bajaj Dominar 250</t>
+  </si>
+  <si>
+    <t>4.5/5 (114 Ratings)</t>
+  </si>
+  <si>
+    <t>248.8 cc|35 kmpl|26.63 bhp|180 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,78,273</t>
+  </si>
+  <si>
+    <t>Bajaj Pulsar N125</t>
+  </si>
+  <si>
+    <t>4.4/5 (38 Ratings)</t>
+  </si>
+  <si>
+    <t>124.58 cc|60 kmpl|11.83 bhp|125 kg</t>
+  </si>
+  <si>
+    <t>₹ 93,668</t>
+  </si>
+  <si>
+    <t>CNG</t>
+  </si>
+  <si>
+    <t>Bajaj Freedom (4.6/5)</t>
+  </si>
+  <si>
+    <t>117 Ratings</t>
+  </si>
+  <si>
+    <t>125 cc|90 km/kg|9.3 bhp|149 kg</t>
+  </si>
+  <si>
+    <t>Bajaj Chetak C2501 (4.4/5)</t>
+  </si>
+  <si>
+    <t>3 Ratings</t>
+  </si>
+  <si>
+    <t>55 kmph|113 km|108 kg|2.5 kWh</t>
+  </si>
+  <si>
+    <t>Bajaj Avenger Cruise 220</t>
+  </si>
+  <si>
+    <t>4.4/5 (341 Ratings)</t>
+  </si>
+  <si>
+    <t>220 cc|39 kmpl|18.76 bhp|163 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,26,620</t>
+  </si>
+  <si>
+    <t>Bajaj Platina 100</t>
+  </si>
+  <si>
+    <t>4.5/5 (522 Ratings)</t>
+  </si>
+  <si>
+    <t>102 cc|75 kmpl|7.79 bhp|117 kg</t>
+  </si>
+  <si>
+    <t>₹ 66,593</t>
+  </si>
+  <si>
+    <t>Bajaj CT 110</t>
+  </si>
+  <si>
+    <t>4.4/5 (115 Ratings)</t>
+  </si>
+  <si>
+    <t>115.45 cc|70 kmpl|8.48 bhp|127 kg</t>
+  </si>
+  <si>
+    <t>₹ 68,050</t>
+  </si>
+  <si>
+    <t>Bajaj Avenger Street 160</t>
+  </si>
+  <si>
+    <t>4.4/5 (151 Ratings)</t>
+  </si>
+  <si>
+    <t>160 cc|45 kmpl|14.79 bhp|156 kg</t>
+  </si>
+  <si>
+    <t>₹ 1,12,280</t>
+  </si>
+  <si>
+    <t>Bajaj Platina 110</t>
+  </si>
+  <si>
+    <t>4.4/5 (170 Ratings)</t>
+  </si>
+  <si>
+    <t>115.45 cc|70 kmpl|8.48 bhp|119 kg</t>
+  </si>
+  <si>
+    <t>₹ 69,941</t>
   </si>
 </sst>
 </file>
@@ -687,168 +931,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
@@ -1704,4 +1786,470 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>273</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>285</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="10"/>
-    <sheet name="Sheet_3" r:id="rId5" sheetId="11"/>
-    <sheet name="Sheet_4" r:id="rId8" sheetId="12"/>
-    <sheet name="Sheet_5" r:id="rId6" sheetId="13"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="14"/>
+    <sheet name="Sheet_3" r:id="rId9" sheetId="15"/>
+    <sheet name="Sheet_4" r:id="rId8" sheetId="16"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="17"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="210">
   <si>
     <t>Sr. No</t>
   </si>
@@ -687,7 +687,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -849,7 +849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -915,7 +915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1421,7 +1421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1442,10 +1442,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>206</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -1453,10 +1453,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -1464,10 +1464,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -1475,10 +1475,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -1486,10 +1486,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1497,10 +1497,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -1508,10 +1508,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>207</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>208</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1519,10 +1519,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -1530,10 +1530,10 @@
         <v>26</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -1541,10 +1541,10 @@
         <v>28</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -1552,10 +1552,10 @@
         <v>30</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -1563,10 +1563,10 @@
         <v>32</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
@@ -1574,10 +1574,10 @@
         <v>34</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -1585,10 +1585,10 @@
         <v>36</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -1596,10 +1596,10 @@
         <v>38</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -1607,10 +1607,10 @@
         <v>40</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -1618,10 +1618,10 @@
         <v>42</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -1629,10 +1629,10 @@
         <v>44</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -1640,10 +1640,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
@@ -1651,10 +1651,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
@@ -1662,10 +1662,10 @@
         <v>86</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23">
@@ -1673,10 +1673,10 @@
         <v>89</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
@@ -1684,10 +1684,10 @@
         <v>91</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -1695,10 +1695,10 @@
         <v>92</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="14"/>
-    <sheet name="Sheet_3" r:id="rId9" sheetId="15"/>
-    <sheet name="Sheet_4" r:id="rId8" sheetId="16"/>
-    <sheet name="Sheet_5" r:id="rId6" sheetId="17"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="30"/>
+    <sheet name="Sheet_3" r:id="rId9" sheetId="31"/>
+    <sheet name="Sheet_4" r:id="rId8" sheetId="32"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="33"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="219">
   <si>
     <t>Sr. No</t>
   </si>
@@ -645,6 +645,33 @@
   </si>
   <si>
     <t>2015 Suzuki Gixxer Single Channel ABS - BS4</t>
+  </si>
+  <si>
+    <t>Yezdi Roadster New Colour Launched at Rs. 2.10 Lakh</t>
+  </si>
+  <si>
+    <t>Suzuki E Access Rentals and Subscription Services Announced</t>
+  </si>
+  <si>
+    <t>MotoGP 2026: Aprilia Racing's Marco Bezzecchi wins the Thailand Grand Prix</t>
+  </si>
+  <si>
+    <t>Ola Offers Holi Delights; Roadster X Starts at Rs. 79,999</t>
+  </si>
+  <si>
+    <t>Yamaha XSR155 Available In Five Colours</t>
+  </si>
+  <si>
+    <t>Studds Thunder Fenix helmet launched at Rs 1,995</t>
+  </si>
+  <si>
+    <t>2016 Suzuki Gixxer Standard</t>
+  </si>
+  <si>
+    <t>₹ 48,500</t>
+  </si>
+  <si>
+    <t>₹ 70,000</t>
   </si>
 </sst>
 </file>
@@ -687,7 +714,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -705,7 +732,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>16</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +740,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>17</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
@@ -721,7 +748,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>18</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>19</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -737,7 +764,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>20</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
@@ -745,7 +772,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>21</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -753,7 +780,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -761,7 +788,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -769,7 +796,7 @@
         <v>26</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -777,7 +804,7 @@
         <v>28</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +812,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -793,7 +820,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -801,7 +828,7 @@
         <v>34</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -809,7 +836,7 @@
         <v>36</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -817,7 +844,7 @@
         <v>38</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -825,7 +852,7 @@
         <v>40</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -833,7 +860,7 @@
         <v>42</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -841,7 +868,7 @@
         <v>44</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -915,7 +942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1421,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="30"/>
-    <sheet name="Sheet_3" r:id="rId9" sheetId="31"/>
-    <sheet name="Sheet_4" r:id="rId8" sheetId="32"/>
-    <sheet name="Sheet_5" r:id="rId6" sheetId="33"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="34"/>
+    <sheet name="Sheet_3" r:id="rId9" sheetId="35"/>
+    <sheet name="Sheet_4" r:id="rId8" sheetId="36"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="37"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="219">
   <si>
     <t>Sr. No</t>
   </si>
@@ -714,7 +714,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -876,7 +876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -942,7 +942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1448,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="30"/>
-    <sheet name="Sheet_3" r:id="rId9" sheetId="31"/>
-    <sheet name="Sheet_4" r:id="rId8" sheetId="32"/>
-    <sheet name="Sheet_5" r:id="rId6" sheetId="33"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="41"/>
+    <sheet name="Sheet_3" r:id="rId9" sheetId="42"/>
+    <sheet name="Sheet_4" r:id="rId8" sheetId="43"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="44"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="219">
   <si>
     <t>Sr. No</t>
   </si>
@@ -714,7 +714,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -876,7 +876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -942,7 +942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1448,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1469,10 +1469,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>51</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
@@ -1480,10 +1480,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -1491,10 +1491,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -1502,10 +1502,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -1513,10 +1513,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1524,10 +1524,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1535,10 +1535,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -1546,10 +1546,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -1557,10 +1557,10 @@
         <v>26</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -1568,10 +1568,10 @@
         <v>28</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -1579,10 +1579,10 @@
         <v>30</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -1590,10 +1590,10 @@
         <v>32</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1601,10 +1601,10 @@
         <v>34</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -1612,10 +1612,10 @@
         <v>36</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -1623,10 +1623,10 @@
         <v>38</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -1634,10 +1634,10 @@
         <v>40</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -1645,10 +1645,10 @@
         <v>42</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1656,10 +1656,10 @@
         <v>44</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,10 +1667,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -1678,10 +1678,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
@@ -1689,10 +1689,10 @@
         <v>86</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
@@ -1700,10 +1700,10 @@
         <v>89</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
@@ -1711,10 +1711,10 @@
         <v>91</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
@@ -1722,10 +1722,10 @@
         <v>92</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="34"/>
-    <sheet name="Sheet_3" r:id="rId9" sheetId="35"/>
-    <sheet name="Sheet_4" r:id="rId8" sheetId="36"/>
-    <sheet name="Sheet_5" r:id="rId6" sheetId="37"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="38"/>
+    <sheet name="Sheet_3" r:id="rId9" sheetId="39"/>
+    <sheet name="Sheet_4" r:id="rId8" sheetId="40"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="41"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="219">
   <si>
     <t>Sr. No</t>
   </si>
@@ -714,7 +714,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -876,7 +876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -942,7 +942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1448,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1469,10 +1469,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>51</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
@@ -1480,10 +1480,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -1491,10 +1491,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -1502,10 +1502,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -1513,10 +1513,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1524,10 +1524,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1535,10 +1535,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -1546,10 +1546,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -1557,10 +1557,10 @@
         <v>26</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -1568,10 +1568,10 @@
         <v>28</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -1579,10 +1579,10 @@
         <v>30</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -1590,10 +1590,10 @@
         <v>32</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1601,10 +1601,10 @@
         <v>34</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -1612,10 +1612,10 @@
         <v>36</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -1623,10 +1623,10 @@
         <v>38</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -1634,10 +1634,10 @@
         <v>40</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -1645,10 +1645,10 @@
         <v>42</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -1656,10 +1656,10 @@
         <v>44</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,10 +1667,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -1678,10 +1678,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
@@ -1689,10 +1689,10 @@
         <v>86</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
@@ -1700,10 +1700,10 @@
         <v>89</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
@@ -1711,10 +1711,10 @@
         <v>91</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
@@ -1722,10 +1722,10 @@
         <v>92</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelData/BikeReport.xlsx
+++ b/ExcelData/BikeReport.xlsx
@@ -6,16 +6,16 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet_2" r:id="rId7" sheetId="38"/>
-    <sheet name="Sheet_3" r:id="rId9" sheetId="39"/>
-    <sheet name="Sheet_4" r:id="rId8" sheetId="40"/>
-    <sheet name="Sheet_5" r:id="rId6" sheetId="41"/>
+    <sheet name="Sheet_2" r:id="rId7" sheetId="42"/>
+    <sheet name="Sheet_4" r:id="rId8" sheetId="43"/>
+    <sheet name="Sheet_5" r:id="rId6" sheetId="44"/>
+    <sheet name="Sheet_3" r:id="rId9" sheetId="45"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="219">
   <si>
     <t>Sr. No</t>
   </si>
@@ -714,7 +714,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -876,7 +876,798 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B62"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>193</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -940,795 +1731,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="B26" t="s" s="0">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="B27" t="s" s="0">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="B28" t="s" s="0">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>137</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="0">
-        <v>147</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="0">
-        <v>153</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="0">
-        <v>155</v>
-      </c>
-      <c r="B38" t="s" s="0">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
-        <v>157</v>
-      </c>
-      <c r="B39" t="s" s="0">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="B40" t="s" s="0">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
-        <v>161</v>
-      </c>
-      <c r="B41" t="s" s="0">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="B42" t="s" s="0">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>165</v>
-      </c>
-      <c r="B43" t="s" s="0">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>167</v>
-      </c>
-      <c r="B44" t="s" s="0">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>169</v>
-      </c>
-      <c r="B45" t="s" s="0">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
-        <v>171</v>
-      </c>
-      <c r="B46" t="s" s="0">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="B47" t="s" s="0">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="0">
-        <v>175</v>
-      </c>
-      <c r="B48" t="s" s="0">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="0">
-        <v>177</v>
-      </c>
-      <c r="B49" t="s" s="0">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="0">
-        <v>179</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="0">
-        <v>181</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="0">
-        <v>183</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="0">
-        <v>185</v>
-      </c>
-      <c r="B53" t="s" s="0">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="0">
-        <v>187</v>
-      </c>
-      <c r="B54" t="s" s="0">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="0">
-        <v>189</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="B56" t="s" s="0">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="0">
-        <v>193</v>
-      </c>
-      <c r="B57" t="s" s="0">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="0">
-        <v>195</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="B59" t="s" s="0">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="0">
-        <v>201</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>204</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B24" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>